--- a/artfynd/A 20438-2026 artfynd.xlsx
+++ b/artfynd/A 20438-2026 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133813720</v>
+        <v>133814300</v>
       </c>
       <c r="B3" t="n">
-        <v>57975</v>
+        <v>91960</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,42 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sellskolningen, Sellskolningen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>494252</v>
+        <v>494285</v>
       </c>
       <c r="R3" t="n">
-        <v>6818338</v>
+        <v>6818294</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,12 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:10</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133814300</v>
+        <v>133813720</v>
       </c>
       <c r="B4" t="n">
-        <v>91960</v>
+        <v>57975</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,37 +900,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Sellskolningen, Sellskolningen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>494285</v>
+        <v>494252</v>
       </c>
       <c r="R4" t="n">
-        <v>6818294</v>
+        <v>6818338</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,7 +974,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1770,50 +1770,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133812855</v>
+        <v>133812590</v>
       </c>
       <c r="B12" t="n">
-        <v>8460</v>
+        <v>79359</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sellskolningen, Sellskolningen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>494355</v>
+        <v>494338</v>
       </c>
       <c r="R12" t="n">
-        <v>6818289</v>
+        <v>6818250</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1856,11 +1851,6 @@
       <c r="AB12" t="inlineStr">
         <is>
           <t>09:28</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Fl träd</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1887,45 +1877,50 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133812590</v>
+        <v>133812855</v>
       </c>
       <c r="B13" t="n">
-        <v>79359</v>
+        <v>8460</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Sellskolningen, Sellskolningen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>494338</v>
+        <v>494355</v>
       </c>
       <c r="R13" t="n">
-        <v>6818250</v>
+        <v>6818289</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1968,6 +1963,11 @@
       <c r="AB13" t="inlineStr">
         <is>
           <t>09:28</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Fl träd</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2773,32 +2773,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133812678</v>
+        <v>133814207</v>
       </c>
       <c r="B21" t="n">
-        <v>93257</v>
+        <v>79359</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2808,10 +2808,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>494364</v>
+        <v>494278</v>
       </c>
       <c r="R21" t="n">
-        <v>6818272</v>
+        <v>6818278</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2843,7 +2843,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2880,32 +2880,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133814207</v>
+        <v>133812678</v>
       </c>
       <c r="B22" t="n">
-        <v>79359</v>
+        <v>93257</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2915,10 +2915,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>494278</v>
+        <v>494364</v>
       </c>
       <c r="R22" t="n">
-        <v>6818278</v>
+        <v>6818272</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2950,7 +2950,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2960,7 +2960,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 20438-2026 artfynd.xlsx
+++ b/artfynd/A 20438-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133814059</v>
       </c>
       <c r="B2" t="n">
-        <v>91910</v>
+        <v>91917</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133814300</v>
+        <v>133813720</v>
       </c>
       <c r="B3" t="n">
-        <v>91960</v>
+        <v>57975</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,37 +793,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sellskolningen, Sellskolningen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>494285</v>
+        <v>494252</v>
       </c>
       <c r="R3" t="n">
-        <v>6818294</v>
+        <v>6818338</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -852,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +867,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133813720</v>
+        <v>133814300</v>
       </c>
       <c r="B4" t="n">
-        <v>57975</v>
+        <v>91967</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,42 +910,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Sellskolningen, Sellskolningen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>494252</v>
+        <v>494285</v>
       </c>
       <c r="R4" t="n">
-        <v>6818338</v>
+        <v>6818294</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -964,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -974,12 +979,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:10</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1121,7 +1121,7 @@
         <v>133812615</v>
       </c>
       <c r="B6" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>133813608</v>
       </c>
       <c r="B7" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>133812878</v>
       </c>
       <c r="B8" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         <v>133813921</v>
       </c>
       <c r="B9" t="n">
-        <v>80479</v>
+        <v>80486</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>133813941</v>
       </c>
       <c r="B10" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1770,45 +1770,50 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133812590</v>
+        <v>133812855</v>
       </c>
       <c r="B12" t="n">
-        <v>79359</v>
+        <v>8460</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sellskolningen, Sellskolningen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>494338</v>
+        <v>494355</v>
       </c>
       <c r="R12" t="n">
-        <v>6818250</v>
+        <v>6818289</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1851,6 +1856,11 @@
       <c r="AB12" t="inlineStr">
         <is>
           <t>09:28</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Fl träd</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1877,50 +1887,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133812855</v>
+        <v>133812590</v>
       </c>
       <c r="B13" t="n">
-        <v>8460</v>
+        <v>79366</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Sellskolningen, Sellskolningen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>494355</v>
+        <v>494338</v>
       </c>
       <c r="R13" t="n">
-        <v>6818289</v>
+        <v>6818250</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1963,11 +1968,6 @@
       <c r="AB13" t="inlineStr">
         <is>
           <t>09:28</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Fl träd</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2221,7 +2221,7 @@
         <v>133813666</v>
       </c>
       <c r="B16" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2328,7 +2328,7 @@
         <v>133814153</v>
       </c>
       <c r="B17" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2537,17 +2537,17 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133813475</v>
+        <v>133813144</v>
       </c>
       <c r="B19" t="n">
-        <v>58461</v>
+        <v>79366</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2555,52 +2555,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103018</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Sellskolningen, Sellskolningen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>494345</v>
+        <v>494351</v>
       </c>
       <c r="R19" t="n">
-        <v>6818345</v>
+        <v>6818323</v>
       </c>
       <c r="S19" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2666,10 +2651,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133813144</v>
+        <v>133813475</v>
       </c>
       <c r="B20" t="n">
-        <v>79359</v>
+        <v>58461</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2677,37 +2662,52 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>103018</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Sellskolningen, Sellskolningen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>494351</v>
+        <v>494345</v>
       </c>
       <c r="R20" t="n">
-        <v>6818323</v>
+        <v>6818345</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2773,32 +2773,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133814207</v>
+        <v>133812678</v>
       </c>
       <c r="B21" t="n">
-        <v>79359</v>
+        <v>93264</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2808,10 +2808,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>494278</v>
+        <v>494364</v>
       </c>
       <c r="R21" t="n">
-        <v>6818278</v>
+        <v>6818272</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2843,7 +2843,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2880,32 +2880,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133812678</v>
+        <v>133814207</v>
       </c>
       <c r="B22" t="n">
-        <v>93257</v>
+        <v>79366</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2915,10 +2915,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>494364</v>
+        <v>494278</v>
       </c>
       <c r="R22" t="n">
-        <v>6818272</v>
+        <v>6818278</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2950,7 +2950,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2960,7 +2960,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 20438-2026 artfynd.xlsx
+++ b/artfynd/A 20438-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133814059</v>
       </c>
       <c r="B2" t="n">
-        <v>91917</v>
+        <v>91924</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133813720</v>
+        <v>133814300</v>
       </c>
       <c r="B3" t="n">
-        <v>57975</v>
+        <v>91974</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,42 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sellskolningen, Sellskolningen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>494252</v>
+        <v>494285</v>
       </c>
       <c r="R3" t="n">
-        <v>6818338</v>
+        <v>6818294</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,12 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:10</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133814300</v>
+        <v>133812678</v>
       </c>
       <c r="B4" t="n">
-        <v>91967</v>
+        <v>93271</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -934,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>494285</v>
+        <v>494364</v>
       </c>
       <c r="R4" t="n">
-        <v>6818294</v>
+        <v>6818272</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,50 +996,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133814244</v>
+        <v>133812558</v>
       </c>
       <c r="B5" t="n">
-        <v>5181</v>
+        <v>79373</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Sellskolningen, Sellskolningen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>494277</v>
+        <v>494338</v>
       </c>
       <c r="R5" t="n">
-        <v>6818294</v>
+        <v>6818250</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1081,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1091,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1121,11 +1106,11 @@
         <v>133812615</v>
       </c>
       <c r="B6" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1225,14 +1210,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133813608</v>
+        <v>133812878</v>
       </c>
       <c r="B7" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1260,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>494271</v>
+        <v>494355</v>
       </c>
       <c r="R7" t="n">
-        <v>6818353</v>
+        <v>6818289</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1295,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1305,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1332,14 +1317,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133812878</v>
+        <v>133813144</v>
       </c>
       <c r="B8" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1367,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>494355</v>
+        <v>494351</v>
       </c>
       <c r="R8" t="n">
-        <v>6818289</v>
+        <v>6818323</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1402,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1412,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1439,32 +1424,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133813921</v>
+        <v>133813608</v>
       </c>
       <c r="B9" t="n">
-        <v>80486</v>
+        <v>79373</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1474,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>494231</v>
+        <v>494271</v>
       </c>
       <c r="R9" t="n">
-        <v>6818317</v>
+        <v>6818353</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1509,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1519,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1546,14 +1531,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133813941</v>
+        <v>133813666</v>
       </c>
       <c r="B10" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1581,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>494231</v>
+        <v>494252</v>
       </c>
       <c r="R10" t="n">
-        <v>6818317</v>
+        <v>6818338</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1616,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1626,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1653,53 +1638,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133813247</v>
+        <v>133813832</v>
       </c>
       <c r="B11" t="n">
-        <v>8460</v>
+        <v>79373</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Sellskolningen, Sellskolningen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>494345</v>
+        <v>494231</v>
       </c>
       <c r="R11" t="n">
-        <v>6818345</v>
+        <v>6818317</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1728,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1738,12 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:48</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Fl träd rikl</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1770,50 +1745,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133812855</v>
+        <v>133814153</v>
       </c>
       <c r="B12" t="n">
-        <v>8460</v>
+        <v>79373</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sellskolningen, Sellskolningen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>494355</v>
+        <v>494277</v>
       </c>
       <c r="R12" t="n">
-        <v>6818289</v>
+        <v>6818294</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1845,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1855,12 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:28</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Fl träd</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1887,14 +1852,14 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133812590</v>
+        <v>133814207</v>
       </c>
       <c r="B13" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1922,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>494338</v>
+        <v>494278</v>
       </c>
       <c r="R13" t="n">
-        <v>6818250</v>
+        <v>6818278</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1957,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1967,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1994,50 +1959,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133813491</v>
+        <v>133813921</v>
       </c>
       <c r="B14" t="n">
-        <v>56539</v>
+        <v>80493</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>206004</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Sellskolningen, Sellskolningen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>494345</v>
+        <v>494231</v>
       </c>
       <c r="R14" t="n">
-        <v>6818345</v>
+        <v>6818317</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2069,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2079,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2106,38 +2066,38 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133813736</v>
+        <v>133813720</v>
       </c>
       <c r="B15" t="n">
-        <v>5181</v>
+        <v>57975</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100526</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2192,6 +2152,11 @@
       <c r="AB15" t="inlineStr">
         <is>
           <t>10:10</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2218,45 +2183,50 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133813666</v>
+        <v>133812822</v>
       </c>
       <c r="B16" t="n">
-        <v>79366</v>
+        <v>57162</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Sellskolningen, Sellskolningen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>494252</v>
+        <v>494355</v>
       </c>
       <c r="R16" t="n">
-        <v>6818338</v>
+        <v>6818289</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2288,7 +2258,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2298,7 +2268,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2325,48 +2295,53 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133814153</v>
+        <v>133813736</v>
       </c>
       <c r="B17" t="n">
-        <v>79366</v>
+        <v>5181</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Sellskolningen, Sellskolningen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>494277</v>
+        <v>494252</v>
       </c>
       <c r="R17" t="n">
-        <v>6818294</v>
+        <v>6818338</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2395,7 +2370,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2405,7 +2380,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2432,10 +2407,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133812822</v>
+        <v>133814244</v>
       </c>
       <c r="B18" t="n">
-        <v>57162</v>
+        <v>5181</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2443,27 +2418,27 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100138</v>
+        <v>100526</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2472,10 +2447,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>494355</v>
+        <v>494277</v>
       </c>
       <c r="R18" t="n">
-        <v>6818289</v>
+        <v>6818294</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2507,7 +2482,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2517,7 +2492,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2544,48 +2519,63 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133813144</v>
+        <v>133813475</v>
       </c>
       <c r="B19" t="n">
-        <v>79366</v>
+        <v>58461</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>103018</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Sellskolningen, Sellskolningen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>494351</v>
+        <v>494345</v>
       </c>
       <c r="R19" t="n">
-        <v>6818323</v>
+        <v>6818345</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2651,48 +2641,38 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133813475</v>
+        <v>133812855</v>
       </c>
       <c r="B20" t="n">
-        <v>58461</v>
+        <v>8460</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103018</v>
+        <v>106545</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2701,13 +2681,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>494345</v>
+        <v>494355</v>
       </c>
       <c r="R20" t="n">
-        <v>6818345</v>
+        <v>6818289</v>
       </c>
       <c r="S20" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2736,7 +2716,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2746,7 +2726,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:28</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Fl träd</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2773,10 +2758,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133812678</v>
+        <v>133813247</v>
       </c>
       <c r="B21" t="n">
-        <v>93264</v>
+        <v>8460</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2784,37 +2769,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Sellskolningen, Sellskolningen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>494364</v>
+        <v>494345</v>
       </c>
       <c r="R21" t="n">
-        <v>6818272</v>
+        <v>6818345</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2843,7 +2833,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2853,7 +2843,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:48</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Fl träd rikl</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2880,10 +2875,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133814207</v>
+        <v>133813491</v>
       </c>
       <c r="B22" t="n">
-        <v>79366</v>
+        <v>56539</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2891,34 +2886,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>206004</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Sellskolningen, Sellskolningen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>494278</v>
+        <v>494345</v>
       </c>
       <c r="R22" t="n">
-        <v>6818278</v>
+        <v>6818345</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2950,7 +2950,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2960,7 +2960,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 20438-2026 artfynd.xlsx
+++ b/artfynd/A 20438-2026 artfynd.xlsx
@@ -2512,7 +2512,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>

--- a/artfynd/A 20438-2026 artfynd.xlsx
+++ b/artfynd/A 20438-2026 artfynd.xlsx
@@ -2512,7 +2512,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>

--- a/artfynd/A 20438-2026 artfynd.xlsx
+++ b/artfynd/A 20438-2026 artfynd.xlsx
@@ -2980,7 +2980,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>

--- a/artfynd/A 20438-2026 artfynd.xlsx
+++ b/artfynd/A 20438-2026 artfynd.xlsx
@@ -882,7 +882,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2980,7 +2980,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>

--- a/artfynd/A 20438-2026 artfynd.xlsx
+++ b/artfynd/A 20438-2026 artfynd.xlsx
@@ -882,7 +882,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>

--- a/artfynd/A 20438-2026 artfynd.xlsx
+++ b/artfynd/A 20438-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AZ22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133814059</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133814300</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133812678</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133812558</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133812615</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133812878</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1421,6 +1456,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133813144</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1528,6 +1568,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133813608</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1635,6 +1680,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133813666</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1742,6 +1792,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133813832</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1849,6 +1904,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133814153</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1956,6 +2016,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133814207</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2063,6 +2128,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133813921</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2180,6 +2250,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133813720</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2292,6 +2367,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133812822</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2404,6 +2484,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133813736</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2516,6 +2601,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133814244</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2638,6 +2728,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133813475</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2755,6 +2850,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133812855</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2872,6 +2972,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133813247</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2984,8 +3089,36 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133813491</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>